--- a/Exercise 4/Data/Day 3/OurSpectrometer.xlsx
+++ b/Exercise 4/Data/Day 3/OurSpectrometer.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AU780411\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42ab932c1675aa28/Dokumenter/GitHub/Labgruppe-Eksperimentiel-Fysik-2/Exercise 4/Data/Day 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55A24893-1617-49F4-AD36-B462594F0BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{55A24893-1617-49F4-AD36-B462594F0BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEAC6054-D116-5324-B42C-81004FF49DCE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{2A1367FC-35DD-4BD7-A8A0-1650767156F6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2A1367FC-35DD-4BD7-A8A0-1650767156F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -111,7 +111,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="da-DK"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1125,7 +1125,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1442,14 +1442,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{485315AB-3007-4923-8BA5-FB5BD9F8F243}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>60</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>124.8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>61</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>126.7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>62</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>173.8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>63</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>314.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>64</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>3231</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>65</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>5182</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>66</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>5185</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>67</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>5183</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>68</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>69</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>364.7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>70</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>195.9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>71</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>218.7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>72</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>261.89999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>73</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>74</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>195.8</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>75</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>180.8</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>75.5</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>273.8</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>76</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>226.5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>77</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>176.2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>78</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>79</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>179.5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>80</v>
       </c>
